--- a/assets/sched.xlsx
+++ b/assets/sched.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amosca/Documents/Smith/teaching/SDS-CSC235/assets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abmosca/Documents/Smith/teaching/SDS-CSC235/SDS-CSC235/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF4F0558-BB6A-F240-8835-AFFF24B0B001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F317805-5790-4940-96D6-E8ACB44C7493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="25300" windowHeight="22860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="25300" windowHeight="15660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sched" sheetId="2" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="52">
   <si>
     <t>Date</t>
   </si>
@@ -185,6 +185,9 @@
   </si>
   <si>
     <t>Communicating Uncertainty and Bias</t>
+  </si>
+  <si>
+    <t>CLASS CANCELED - Snow Day</t>
   </si>
 </sst>
 </file>
@@ -356,7 +359,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -432,12 +435,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -688,27 +692,31 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A2" s="13"/>
-      <c r="B2" s="15"/>
+      <c r="A2" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>5</v>
+      </c>
       <c r="C2" s="48">
         <v>1</v>
       </c>
-      <c r="D2" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="26">
+      <c r="D2" s="43" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="44">
         <v>45684</v>
       </c>
-      <c r="F2" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="8"/>
-      <c r="H2" s="27"/>
+      <c r="F2" s="45" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" s="46"/>
+      <c r="H2" s="51"/>
     </row>
     <row r="3" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A3" s="14"/>
       <c r="B3" s="16"/>
-      <c r="C3" s="49"/>
+      <c r="C3" s="50"/>
       <c r="D3" s="28" t="s">
         <v>12</v>
       </c>
@@ -716,7 +724,7 @@
         <v>45686</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G3" s="16" t="s">
         <v>43</v>
@@ -736,7 +744,7 @@
         <v>45691</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="G4" s="8"/>
       <c r="H4" s="33"/>
@@ -744,7 +752,7 @@
     <row r="5" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9"/>
       <c r="B5" s="16"/>
-      <c r="C5" s="49"/>
+      <c r="C5" s="50"/>
       <c r="D5" s="28" t="s">
         <v>12</v>
       </c>
@@ -752,7 +760,7 @@
         <v>45693</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="G5" s="16" t="s">
         <v>44</v>
@@ -774,14 +782,14 @@
         <v>45698</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G6" s="8"/>
       <c r="H6" s="27"/>
     </row>
     <row r="7" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9"/>
-      <c r="C7" s="49"/>
+      <c r="C7" s="50"/>
       <c r="D7" s="28" t="s">
         <v>12</v>
       </c>
@@ -789,7 +797,7 @@
         <v>45700</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G7" s="16" t="s">
         <v>45</v>
@@ -811,14 +819,14 @@
         <v>45705</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G8" s="8"/>
       <c r="H8" s="27"/>
     </row>
     <row r="9" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9"/>
-      <c r="C9" s="49"/>
+      <c r="C9" s="50"/>
       <c r="D9" s="28" t="s">
         <v>12</v>
       </c>
@@ -826,7 +834,7 @@
         <v>45707</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G9" s="16" t="s">
         <v>42</v>
@@ -849,8 +857,8 @@
       <c r="E10" s="26">
         <v>45712</v>
       </c>
-      <c r="F10" s="32" t="s">
-        <v>26</v>
+      <c r="F10" s="15" t="s">
+        <v>24</v>
       </c>
       <c r="G10" s="8"/>
       <c r="H10" s="27"/>
@@ -862,7 +870,7 @@
       <c r="B11" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="49"/>
+      <c r="C11" s="50"/>
       <c r="D11" s="37" t="s">
         <v>12</v>
       </c>
@@ -892,14 +900,14 @@
         <v>45719</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G12" s="8"/>
       <c r="H12" s="27"/>
     </row>
     <row r="13" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9"/>
-      <c r="C13" s="49"/>
+      <c r="C13" s="50"/>
       <c r="D13" s="28" t="s">
         <v>12</v>
       </c>
@@ -907,7 +915,7 @@
         <v>45721</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G13" s="16"/>
       <c r="H13" s="31"/>
@@ -933,7 +941,7 @@
     <row r="15" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A15" s="14"/>
       <c r="B15" s="16"/>
-      <c r="C15" s="49"/>
+      <c r="C15" s="50"/>
       <c r="D15" s="28" t="s">
         <v>12</v>
       </c>
@@ -979,7 +987,7 @@
       <c r="B17" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="49"/>
+      <c r="C17" s="50"/>
       <c r="D17" s="37" t="s">
         <v>12</v>
       </c>
@@ -1013,7 +1021,7 @@
     <row r="19" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A19" s="21"/>
       <c r="B19" s="20"/>
-      <c r="C19" s="50"/>
+      <c r="C19" s="49"/>
       <c r="D19" s="34" t="s">
         <v>12</v>
       </c>
@@ -1055,7 +1063,7 @@
       <c r="B21" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="50"/>
+      <c r="C21" s="49"/>
       <c r="D21" s="34" t="s">
         <v>12</v>
       </c>
@@ -1095,7 +1103,7 @@
       <c r="B23" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C23" s="50"/>
+      <c r="C23" s="49"/>
       <c r="D23" s="40" t="s">
         <v>12</v>
       </c>
@@ -1135,7 +1143,7 @@
       <c r="B25" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="50"/>
+      <c r="C25" s="49"/>
       <c r="D25" s="40" t="s">
         <v>12</v>
       </c>
@@ -1175,7 +1183,7 @@
       <c r="B27" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="50"/>
+      <c r="C27" s="49"/>
       <c r="D27" s="40" t="s">
         <v>12</v>
       </c>
@@ -1219,7 +1227,7 @@
       <c r="B29" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C29" s="50"/>
+      <c r="C29" s="49"/>
       <c r="D29" s="40" t="s">
         <v>12</v>
       </c>
@@ -1247,7 +1255,7 @@
     <row r="31" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
-      <c r="C31" s="50"/>
+      <c r="C31" s="49"/>
       <c r="D31" s="18"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
@@ -1256,6 +1264,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="C10:C11"/>
     <mergeCell ref="C26:C27"/>
     <mergeCell ref="C28:C29"/>
     <mergeCell ref="C30:C31"/>
@@ -1265,12 +1279,6 @@
     <mergeCell ref="C20:C21"/>
     <mergeCell ref="C22:C23"/>
     <mergeCell ref="C24:C25"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="C10:C11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/assets/sched.xlsx
+++ b/assets/sched.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abmosca/Documents/Smith/teaching/SDS-CSC235/SDS-CSC235/assets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amosca/Documents/Smith/teaching/SDS-CSC235/SDS-CSC235/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F317805-5790-4940-96D6-E8ACB44C7493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54C15918-9E96-824E-862E-651E4DBBAAD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="25300" windowHeight="15660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22980" yWindow="500" windowWidth="21880" windowHeight="22200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sched" sheetId="2" r:id="rId1"/>
@@ -97,15 +97,9 @@
     <t>Interactive Visualizations (d3.js)</t>
   </si>
   <si>
-    <t>Geospatial Data Analysis</t>
-  </si>
-  <si>
     <t>Network Data Analysis</t>
   </si>
   <si>
-    <t>Geospatial Lab</t>
-  </si>
-  <si>
     <t>Network Lab</t>
   </si>
   <si>
@@ -188,6 +182,12 @@
   </si>
   <si>
     <t>CLASS CANCELED - Snow Day</t>
+  </si>
+  <si>
+    <t>Geospatial Data Analysis (with SAL)</t>
+  </si>
+  <si>
+    <t>Geospatial Lab (with SAL)</t>
   </si>
 </sst>
 </file>
@@ -432,16 +432,16 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -698,7 +698,7 @@
       <c r="B2" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="48">
+      <c r="C2" s="49">
         <v>1</v>
       </c>
       <c r="D2" s="43" t="s">
@@ -708,10 +708,10 @@
         <v>45684</v>
       </c>
       <c r="F2" s="45" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G2" s="46"/>
-      <c r="H2" s="51"/>
+      <c r="H2" s="48"/>
     </row>
     <row r="3" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A3" s="14"/>
@@ -727,14 +727,14 @@
         <v>18</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H3" s="30"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A4" s="7"/>
       <c r="B4" s="15"/>
-      <c r="C4" s="48">
+      <c r="C4" s="49">
         <v>2</v>
       </c>
       <c r="D4" s="25" t="s">
@@ -760,19 +760,19 @@
         <v>45693</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H5" s="31" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A6" s="7"/>
       <c r="B6" s="15"/>
-      <c r="C6" s="48">
+      <c r="C6" s="49">
         <v>3</v>
       </c>
       <c r="D6" s="25" t="s">
@@ -782,7 +782,7 @@
         <v>45698</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G6" s="8"/>
       <c r="H6" s="27"/>
@@ -800,16 +800,16 @@
         <v>19</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H7" s="31" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A8" s="7"/>
       <c r="B8" s="8"/>
-      <c r="C8" s="48">
+      <c r="C8" s="49">
         <v>4</v>
       </c>
       <c r="D8" s="25" t="s">
@@ -834,13 +834,13 @@
         <v>45707</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H9" s="31" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.15">
@@ -848,7 +848,7 @@
       <c r="B10" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="48">
+      <c r="C10" s="49">
         <v>5</v>
       </c>
       <c r="D10" s="25" t="s">
@@ -858,7 +858,7 @@
         <v>45712</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G10" s="8"/>
       <c r="H10" s="27"/>
@@ -881,16 +881,16 @@
         <v>15</v>
       </c>
       <c r="G11" s="24" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H11" s="39" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A12" s="7"/>
       <c r="B12" s="8"/>
-      <c r="C12" s="48">
+      <c r="C12" s="49">
         <v>6</v>
       </c>
       <c r="D12" s="25" t="s">
@@ -900,7 +900,7 @@
         <v>45719</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="G12" s="8"/>
       <c r="H12" s="27"/>
@@ -915,7 +915,7 @@
         <v>45721</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="G13" s="16"/>
       <c r="H13" s="31"/>
@@ -923,7 +923,7 @@
     <row r="14" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A14" s="13"/>
       <c r="B14" s="15"/>
-      <c r="C14" s="48">
+      <c r="C14" s="49">
         <v>7</v>
       </c>
       <c r="D14" s="25" t="s">
@@ -933,7 +933,7 @@
         <v>45726</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G14" s="8"/>
       <c r="H14" s="27"/>
@@ -949,13 +949,13 @@
         <v>45728</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H15" s="31" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.15">
@@ -965,7 +965,7 @@
       <c r="B16" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="48">
+      <c r="C16" s="49">
         <v>8</v>
       </c>
       <c r="D16" s="43" t="s">
@@ -1003,7 +1003,7 @@
     <row r="18" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A18" s="7"/>
       <c r="B18" s="15"/>
-      <c r="C18" s="48">
+      <c r="C18" s="49">
         <v>9</v>
       </c>
       <c r="D18" s="25" t="s">
@@ -1013,7 +1013,7 @@
         <v>45740</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G18" s="8"/>
       <c r="H18" s="27"/>
@@ -1021,7 +1021,7 @@
     <row r="19" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A19" s="21"/>
       <c r="B19" s="20"/>
-      <c r="C19" s="49"/>
+      <c r="C19" s="51"/>
       <c r="D19" s="34" t="s">
         <v>12</v>
       </c>
@@ -1029,20 +1029,20 @@
         <v>45742</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G19" s="20" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H19" s="36" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I19" s="9"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A20" s="7"/>
       <c r="B20" s="8"/>
-      <c r="C20" s="48">
+      <c r="C20" s="49">
         <v>10</v>
       </c>
       <c r="D20" s="25" t="s">
@@ -1052,7 +1052,7 @@
         <v>45747</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G20" s="8"/>
       <c r="H20" s="27"/>
@@ -1063,7 +1063,7 @@
       <c r="B21" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="49"/>
+      <c r="C21" s="51"/>
       <c r="D21" s="34" t="s">
         <v>12</v>
       </c>
@@ -1071,19 +1071,19 @@
         <v>45749</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G21" s="20" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H21" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A22" s="13"/>
       <c r="B22" s="15"/>
-      <c r="C22" s="48">
+      <c r="C22" s="49">
         <v>11</v>
       </c>
       <c r="D22" s="25" t="s">
@@ -1093,7 +1093,7 @@
         <v>45754</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G22" s="8"/>
       <c r="H22" s="27"/>
@@ -1103,7 +1103,7 @@
       <c r="B23" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C23" s="49"/>
+      <c r="C23" s="51"/>
       <c r="D23" s="40" t="s">
         <v>12</v>
       </c>
@@ -1111,19 +1111,19 @@
         <v>45756</v>
       </c>
       <c r="F23" s="23" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G23" s="23" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H23" s="42" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A24" s="7"/>
       <c r="B24" s="8"/>
-      <c r="C24" s="48">
+      <c r="C24" s="49">
         <v>12</v>
       </c>
       <c r="D24" s="25" t="s">
@@ -1133,7 +1133,7 @@
         <v>45761</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G24" s="15"/>
       <c r="H24" s="27"/>
@@ -1143,7 +1143,7 @@
       <c r="B25" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="49"/>
+      <c r="C25" s="51"/>
       <c r="D25" s="40" t="s">
         <v>12</v>
       </c>
@@ -1151,19 +1151,19 @@
         <v>45763</v>
       </c>
       <c r="F25" s="23" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G25" s="23" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H25" s="42" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A26" s="7"/>
       <c r="B26" s="15"/>
-      <c r="C26" s="48">
+      <c r="C26" s="49">
         <v>13</v>
       </c>
       <c r="D26" s="25" t="s">
@@ -1173,7 +1173,7 @@
         <v>45768</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G26" s="15"/>
       <c r="H26" s="33"/>
@@ -1183,7 +1183,7 @@
       <c r="B27" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="49"/>
+      <c r="C27" s="51"/>
       <c r="D27" s="40" t="s">
         <v>12</v>
       </c>
@@ -1191,13 +1191,13 @@
         <v>45770</v>
       </c>
       <c r="F27" s="23" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G27" s="23" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H27" s="42" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.15">
@@ -1205,7 +1205,7 @@
       <c r="B28" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C28" s="48">
+      <c r="C28" s="49">
         <v>14</v>
       </c>
       <c r="D28" s="25" t="s">
@@ -1215,7 +1215,7 @@
         <v>45775</v>
       </c>
       <c r="F28" s="32" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G28" s="15"/>
       <c r="H28" s="33"/>
@@ -1227,7 +1227,7 @@
       <c r="B29" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C29" s="49"/>
+      <c r="C29" s="51"/>
       <c r="D29" s="40" t="s">
         <v>12</v>
       </c>
@@ -1239,13 +1239,13 @@
       </c>
       <c r="G29" s="23"/>
       <c r="H29" s="42" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A30" s="13"/>
       <c r="B30" s="15"/>
-      <c r="C30" s="48"/>
+      <c r="C30" s="49"/>
       <c r="D30" s="25"/>
       <c r="E30" s="26"/>
       <c r="F30" s="15"/>
@@ -1255,7 +1255,7 @@
     <row r="31" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
-      <c r="C31" s="49"/>
+      <c r="C31" s="51"/>
       <c r="D31" s="18"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
@@ -1264,12 +1264,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="C10:C11"/>
     <mergeCell ref="C26:C27"/>
     <mergeCell ref="C28:C29"/>
     <mergeCell ref="C30:C31"/>
@@ -1279,6 +1273,12 @@
     <mergeCell ref="C20:C21"/>
     <mergeCell ref="C22:C23"/>
     <mergeCell ref="C24:C25"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="C10:C11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/assets/sched.xlsx
+++ b/assets/sched.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amosca/Documents/Smith/teaching/SDS-CSC235/SDS-CSC235/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54C15918-9E96-824E-862E-651E4DBBAAD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8BEC65D-22D0-E143-854F-0AA08E4634A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22980" yWindow="500" windowWidth="21880" windowHeight="22200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1280" yWindow="1880" windowWidth="21880" windowHeight="22200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sched" sheetId="2" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="51">
   <si>
     <t>Date</t>
   </si>
@@ -170,9 +170,6 @@
   </si>
   <si>
     <t>hw04</t>
-  </si>
-  <si>
-    <t>hw05</t>
   </si>
   <si>
     <t>Uncertainty and Bias Lab</t>
@@ -436,10 +433,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -708,7 +705,7 @@
         <v>45684</v>
       </c>
       <c r="F2" s="45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G2" s="46"/>
       <c r="H2" s="48"/>
@@ -716,7 +713,7 @@
     <row r="3" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A3" s="14"/>
       <c r="B3" s="16"/>
-      <c r="C3" s="50"/>
+      <c r="C3" s="51"/>
       <c r="D3" s="28" t="s">
         <v>12</v>
       </c>
@@ -752,7 +749,7 @@
     <row r="5" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9"/>
       <c r="B5" s="16"/>
-      <c r="C5" s="50"/>
+      <c r="C5" s="51"/>
       <c r="D5" s="28" t="s">
         <v>12</v>
       </c>
@@ -789,7 +786,7 @@
     </row>
     <row r="7" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9"/>
-      <c r="C7" s="50"/>
+      <c r="C7" s="51"/>
       <c r="D7" s="28" t="s">
         <v>12</v>
       </c>
@@ -826,7 +823,7 @@
     </row>
     <row r="9" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9"/>
-      <c r="C9" s="50"/>
+      <c r="C9" s="51"/>
       <c r="D9" s="28" t="s">
         <v>12</v>
       </c>
@@ -870,7 +867,7 @@
       <c r="B11" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="50"/>
+      <c r="C11" s="51"/>
       <c r="D11" s="37" t="s">
         <v>12</v>
       </c>
@@ -900,14 +897,14 @@
         <v>45719</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G12" s="8"/>
       <c r="H12" s="27"/>
     </row>
     <row r="13" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9"/>
-      <c r="C13" s="50"/>
+      <c r="C13" s="51"/>
       <c r="D13" s="28" t="s">
         <v>12</v>
       </c>
@@ -915,7 +912,7 @@
         <v>45721</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G13" s="16"/>
       <c r="H13" s="31"/>
@@ -933,7 +930,7 @@
         <v>45726</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G14" s="8"/>
       <c r="H14" s="27"/>
@@ -941,7 +938,7 @@
     <row r="15" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A15" s="14"/>
       <c r="B15" s="16"/>
-      <c r="C15" s="50"/>
+      <c r="C15" s="51"/>
       <c r="D15" s="28" t="s">
         <v>12</v>
       </c>
@@ -949,11 +946,9 @@
         <v>45728</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="G15" s="16" t="s">
-        <v>45</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="G15" s="16"/>
       <c r="H15" s="31" t="s">
         <v>44</v>
       </c>
@@ -987,7 +982,7 @@
       <c r="B17" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="50"/>
+      <c r="C17" s="51"/>
       <c r="D17" s="37" t="s">
         <v>12</v>
       </c>
@@ -1015,13 +1010,15 @@
       <c r="F18" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="G18" s="8"/>
+      <c r="G18" s="15" t="s">
+        <v>45</v>
+      </c>
       <c r="H18" s="27"/>
     </row>
     <row r="19" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A19" s="21"/>
       <c r="B19" s="20"/>
-      <c r="C19" s="51"/>
+      <c r="C19" s="50"/>
       <c r="D19" s="34" t="s">
         <v>12</v>
       </c>
@@ -1031,12 +1028,8 @@
       <c r="F19" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="G19" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="H19" s="36" t="s">
-        <v>45</v>
-      </c>
+      <c r="G19" s="20"/>
+      <c r="H19" s="36"/>
       <c r="I19" s="9"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.15">
@@ -1063,7 +1056,7 @@
       <c r="B21" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="51"/>
+      <c r="C21" s="50"/>
       <c r="D21" s="34" t="s">
         <v>12</v>
       </c>
@@ -1077,7 +1070,7 @@
         <v>30</v>
       </c>
       <c r="H21" s="36" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.15">
@@ -1103,7 +1096,7 @@
       <c r="B23" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C23" s="51"/>
+      <c r="C23" s="50"/>
       <c r="D23" s="40" t="s">
         <v>12</v>
       </c>
@@ -1143,7 +1136,7 @@
       <c r="B25" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="51"/>
+      <c r="C25" s="50"/>
       <c r="D25" s="40" t="s">
         <v>12</v>
       </c>
@@ -1183,7 +1176,7 @@
       <c r="B27" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="51"/>
+      <c r="C27" s="50"/>
       <c r="D27" s="40" t="s">
         <v>12</v>
       </c>
@@ -1227,7 +1220,7 @@
       <c r="B29" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C29" s="51"/>
+      <c r="C29" s="50"/>
       <c r="D29" s="40" t="s">
         <v>12</v>
       </c>
@@ -1255,7 +1248,7 @@
     <row r="31" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
-      <c r="C31" s="51"/>
+      <c r="C31" s="50"/>
       <c r="D31" s="18"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
@@ -1264,6 +1257,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="C10:C11"/>
     <mergeCell ref="C26:C27"/>
     <mergeCell ref="C28:C29"/>
     <mergeCell ref="C30:C31"/>
@@ -1273,12 +1272,6 @@
     <mergeCell ref="C20:C21"/>
     <mergeCell ref="C22:C23"/>
     <mergeCell ref="C24:C25"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="C10:C11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/assets/sched.xlsx
+++ b/assets/sched.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amosca/Documents/Smith/teaching/SDS-CSC235/SDS-CSC235/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8BEC65D-22D0-E143-854F-0AA08E4634A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3E04AD6-D174-E346-8E98-75B0D0ED29B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1280" yWindow="1880" windowWidth="21880" windowHeight="22200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1280" yWindow="1300" windowWidth="21880" windowHeight="22200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sched" sheetId="2" r:id="rId1"/>
@@ -433,10 +433,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -713,7 +713,7 @@
     <row r="3" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A3" s="14"/>
       <c r="B3" s="16"/>
-      <c r="C3" s="51"/>
+      <c r="C3" s="50"/>
       <c r="D3" s="28" t="s">
         <v>12</v>
       </c>
@@ -749,7 +749,7 @@
     <row r="5" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9"/>
       <c r="B5" s="16"/>
-      <c r="C5" s="51"/>
+      <c r="C5" s="50"/>
       <c r="D5" s="28" t="s">
         <v>12</v>
       </c>
@@ -786,7 +786,7 @@
     </row>
     <row r="7" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9"/>
-      <c r="C7" s="51"/>
+      <c r="C7" s="50"/>
       <c r="D7" s="28" t="s">
         <v>12</v>
       </c>
@@ -823,7 +823,7 @@
     </row>
     <row r="9" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9"/>
-      <c r="C9" s="51"/>
+      <c r="C9" s="50"/>
       <c r="D9" s="28" t="s">
         <v>12</v>
       </c>
@@ -867,7 +867,7 @@
       <c r="B11" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="51"/>
+      <c r="C11" s="50"/>
       <c r="D11" s="37" t="s">
         <v>12</v>
       </c>
@@ -904,7 +904,7 @@
     </row>
     <row r="13" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9"/>
-      <c r="C13" s="51"/>
+      <c r="C13" s="50"/>
       <c r="D13" s="28" t="s">
         <v>12</v>
       </c>
@@ -938,7 +938,7 @@
     <row r="15" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A15" s="14"/>
       <c r="B15" s="16"/>
-      <c r="C15" s="51"/>
+      <c r="C15" s="50"/>
       <c r="D15" s="28" t="s">
         <v>12</v>
       </c>
@@ -948,7 +948,9 @@
       <c r="F15" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="G15" s="16"/>
+      <c r="G15" s="16" t="s">
+        <v>45</v>
+      </c>
       <c r="H15" s="31" t="s">
         <v>44</v>
       </c>
@@ -982,7 +984,7 @@
       <c r="B17" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="51"/>
+      <c r="C17" s="50"/>
       <c r="D17" s="37" t="s">
         <v>12</v>
       </c>
@@ -1010,15 +1012,13 @@
       <c r="F18" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="G18" s="15" t="s">
-        <v>45</v>
-      </c>
+      <c r="G18" s="15"/>
       <c r="H18" s="27"/>
     </row>
     <row r="19" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A19" s="21"/>
       <c r="B19" s="20"/>
-      <c r="C19" s="50"/>
+      <c r="C19" s="51"/>
       <c r="D19" s="34" t="s">
         <v>12</v>
       </c>
@@ -1056,7 +1056,7 @@
       <c r="B21" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="50"/>
+      <c r="C21" s="51"/>
       <c r="D21" s="34" t="s">
         <v>12</v>
       </c>
@@ -1096,7 +1096,7 @@
       <c r="B23" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C23" s="50"/>
+      <c r="C23" s="51"/>
       <c r="D23" s="40" t="s">
         <v>12</v>
       </c>
@@ -1136,7 +1136,7 @@
       <c r="B25" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="50"/>
+      <c r="C25" s="51"/>
       <c r="D25" s="40" t="s">
         <v>12</v>
       </c>
@@ -1176,7 +1176,7 @@
       <c r="B27" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="50"/>
+      <c r="C27" s="51"/>
       <c r="D27" s="40" t="s">
         <v>12</v>
       </c>
@@ -1220,7 +1220,7 @@
       <c r="B29" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C29" s="50"/>
+      <c r="C29" s="51"/>
       <c r="D29" s="40" t="s">
         <v>12</v>
       </c>
@@ -1248,7 +1248,7 @@
     <row r="31" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
-      <c r="C31" s="50"/>
+      <c r="C31" s="51"/>
       <c r="D31" s="18"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
@@ -1257,12 +1257,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="C10:C11"/>
     <mergeCell ref="C26:C27"/>
     <mergeCell ref="C28:C29"/>
     <mergeCell ref="C30:C31"/>
@@ -1272,6 +1266,12 @@
     <mergeCell ref="C20:C21"/>
     <mergeCell ref="C22:C23"/>
     <mergeCell ref="C24:C25"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="C10:C11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/assets/sched.xlsx
+++ b/assets/sched.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amosca/Documents/Smith/teaching/SDS-CSC235/SDS-CSC235/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3E04AD6-D174-E346-8E98-75B0D0ED29B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{864F606A-7609-BF4A-8D35-1161719BE513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1280" yWindow="1300" windowWidth="21880" windowHeight="22200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -136,21 +136,9 @@
     <t xml:space="preserve">Final Project Workshop - User Testing </t>
   </si>
   <si>
-    <t xml:space="preserve">Explainable AI / ML </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Explainable AI / ML Lab </t>
-  </si>
-  <si>
-    <t>EMA Lab</t>
-  </si>
-  <si>
     <t>Exploratory Data Analysis (EDA)</t>
   </si>
   <si>
-    <t xml:space="preserve">Exploratory Model Analysis (EMA) </t>
-  </si>
-  <si>
     <t xml:space="preserve">Final Project Introduction </t>
   </si>
   <si>
@@ -185,6 +173,18 @@
   </si>
   <si>
     <t>Geospatial Lab (with SAL)</t>
+  </si>
+  <si>
+    <t>Explainable AI (XAI)</t>
+  </si>
+  <si>
+    <t>XAI Lab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems for Modeling </t>
+  </si>
+  <si>
+    <t>Modeling Lab</t>
   </si>
 </sst>
 </file>
@@ -705,7 +705,7 @@
         <v>45684</v>
       </c>
       <c r="F2" s="45" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G2" s="46"/>
       <c r="H2" s="48"/>
@@ -724,7 +724,7 @@
         <v>18</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H3" s="30"/>
     </row>
@@ -757,13 +757,13 @@
         <v>45693</v>
       </c>
       <c r="F5" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5" s="31" t="s">
         <v>37</v>
-      </c>
-      <c r="G5" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="H5" s="31" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.15">
@@ -797,10 +797,10 @@
         <v>19</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="H7" s="31" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.15">
@@ -834,10 +834,10 @@
         <v>21</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H9" s="31" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.15">
@@ -878,10 +878,10 @@
         <v>15</v>
       </c>
       <c r="G11" s="24" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="H11" s="39" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.15">
@@ -897,7 +897,7 @@
         <v>45719</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G12" s="8"/>
       <c r="H12" s="27"/>
@@ -912,7 +912,7 @@
         <v>45721</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G13" s="16"/>
       <c r="H13" s="31"/>
@@ -930,7 +930,7 @@
         <v>45726</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G14" s="8"/>
       <c r="H14" s="27"/>
@@ -946,13 +946,13 @@
         <v>45728</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="H15" s="31" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.15">
@@ -1045,7 +1045,7 @@
         <v>45747</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="G20" s="8"/>
       <c r="H20" s="27"/>
@@ -1064,13 +1064,13 @@
         <v>45749</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G21" s="20" t="s">
         <v>30</v>
       </c>
       <c r="H21" s="36" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.15">
@@ -1086,7 +1086,7 @@
         <v>45754</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="G22" s="8"/>
       <c r="H22" s="27"/>
@@ -1126,7 +1126,7 @@
         <v>45761</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="G24" s="15"/>
       <c r="H24" s="27"/>
@@ -1166,7 +1166,7 @@
         <v>45768</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="G26" s="15"/>
       <c r="H26" s="33"/>

--- a/assets/sched.xlsx
+++ b/assets/sched.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amosca/Documents/Smith/teaching/SDS-CSC235/SDS-CSC235/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{864F606A-7609-BF4A-8D35-1161719BE513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB0C2C6B-A930-D343-91B1-02F5E16E249A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1280" yWindow="1300" windowWidth="21880" windowHeight="22200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1280" yWindow="1300" windowWidth="24200" windowHeight="22180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sched" sheetId="2" r:id="rId1"/>
@@ -127,15 +127,6 @@
     <t>fp01</t>
   </si>
   <si>
-    <t>Final Project Workshop - Proposal Check-in</t>
-  </si>
-  <si>
-    <t>Final Project Workshop - Prototype Testing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final Project Workshop - User Testing </t>
-  </si>
-  <si>
     <t>Exploratory Data Analysis (EDA)</t>
   </si>
   <si>
@@ -185,6 +176,15 @@
   </si>
   <si>
     <t>Modeling Lab</t>
+  </si>
+  <si>
+    <t>Final Project Workshop - Plan Check-in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final Project Workshop - Feedback Modifications  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final Project Workshop - User Testing Prep </t>
   </si>
 </sst>
 </file>
@@ -433,10 +433,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -705,7 +705,7 @@
         <v>45684</v>
       </c>
       <c r="F2" s="45" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G2" s="46"/>
       <c r="H2" s="48"/>
@@ -713,7 +713,7 @@
     <row r="3" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A3" s="14"/>
       <c r="B3" s="16"/>
-      <c r="C3" s="50"/>
+      <c r="C3" s="51"/>
       <c r="D3" s="28" t="s">
         <v>12</v>
       </c>
@@ -724,7 +724,7 @@
         <v>18</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H3" s="30"/>
     </row>
@@ -749,7 +749,7 @@
     <row r="5" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9"/>
       <c r="B5" s="16"/>
-      <c r="C5" s="50"/>
+      <c r="C5" s="51"/>
       <c r="D5" s="28" t="s">
         <v>12</v>
       </c>
@@ -757,13 +757,13 @@
         <v>45693</v>
       </c>
       <c r="F5" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" s="31" t="s">
         <v>34</v>
-      </c>
-      <c r="G5" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="H5" s="31" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.15">
@@ -786,7 +786,7 @@
     </row>
     <row r="7" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9"/>
-      <c r="C7" s="50"/>
+      <c r="C7" s="51"/>
       <c r="D7" s="28" t="s">
         <v>12</v>
       </c>
@@ -797,10 +797,10 @@
         <v>19</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H7" s="31" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.15">
@@ -823,7 +823,7 @@
     </row>
     <row r="9" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9"/>
-      <c r="C9" s="50"/>
+      <c r="C9" s="51"/>
       <c r="D9" s="28" t="s">
         <v>12</v>
       </c>
@@ -834,10 +834,10 @@
         <v>21</v>
       </c>
       <c r="G9" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9" s="31" t="s">
         <v>36</v>
-      </c>
-      <c r="H9" s="31" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.15">
@@ -867,7 +867,7 @@
       <c r="B11" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="50"/>
+      <c r="C11" s="51"/>
       <c r="D11" s="37" t="s">
         <v>12</v>
       </c>
@@ -878,10 +878,10 @@
         <v>15</v>
       </c>
       <c r="G11" s="24" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H11" s="39" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.15">
@@ -897,14 +897,14 @@
         <v>45719</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G12" s="8"/>
       <c r="H12" s="27"/>
     </row>
     <row r="13" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9"/>
-      <c r="C13" s="50"/>
+      <c r="C13" s="51"/>
       <c r="D13" s="28" t="s">
         <v>12</v>
       </c>
@@ -912,7 +912,7 @@
         <v>45721</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G13" s="16"/>
       <c r="H13" s="31"/>
@@ -930,7 +930,7 @@
         <v>45726</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G14" s="8"/>
       <c r="H14" s="27"/>
@@ -938,7 +938,7 @@
     <row r="15" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A15" s="14"/>
       <c r="B15" s="16"/>
-      <c r="C15" s="50"/>
+      <c r="C15" s="51"/>
       <c r="D15" s="28" t="s">
         <v>12</v>
       </c>
@@ -946,13 +946,13 @@
         <v>45728</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H15" s="31" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.15">
@@ -984,7 +984,7 @@
       <c r="B17" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="50"/>
+      <c r="C17" s="51"/>
       <c r="D17" s="37" t="s">
         <v>12</v>
       </c>
@@ -1018,7 +1018,7 @@
     <row r="19" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A19" s="21"/>
       <c r="B19" s="20"/>
-      <c r="C19" s="51"/>
+      <c r="C19" s="50"/>
       <c r="D19" s="34" t="s">
         <v>12</v>
       </c>
@@ -1045,7 +1045,7 @@
         <v>45747</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G20" s="8"/>
       <c r="H20" s="27"/>
@@ -1056,21 +1056,21 @@
       <c r="B21" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="51"/>
-      <c r="D21" s="34" t="s">
-        <v>12</v>
-      </c>
-      <c r="E21" s="35">
+      <c r="C21" s="50"/>
+      <c r="D21" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" s="41">
         <v>45749</v>
       </c>
-      <c r="F21" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="G21" s="20" t="s">
+      <c r="F21" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="H21" s="36" t="s">
-        <v>41</v>
+      <c r="H21" s="42" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.15">
@@ -1086,7 +1086,7 @@
         <v>45754</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G22" s="8"/>
       <c r="H22" s="27"/>
@@ -1096,7 +1096,7 @@
       <c r="B23" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C23" s="51"/>
+      <c r="C23" s="50"/>
       <c r="D23" s="40" t="s">
         <v>12</v>
       </c>
@@ -1104,7 +1104,7 @@
         <v>45756</v>
       </c>
       <c r="F23" s="23" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="G23" s="23" t="s">
         <v>29</v>
@@ -1126,7 +1126,7 @@
         <v>45761</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G24" s="15"/>
       <c r="H24" s="27"/>
@@ -1136,7 +1136,7 @@
       <c r="B25" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="51"/>
+      <c r="C25" s="50"/>
       <c r="D25" s="40" t="s">
         <v>12</v>
       </c>
@@ -1144,7 +1144,7 @@
         <v>45763</v>
       </c>
       <c r="F25" s="23" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="G25" s="23" t="s">
         <v>28</v>
@@ -1166,7 +1166,7 @@
         <v>45768</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G26" s="15"/>
       <c r="H26" s="33"/>
@@ -1176,7 +1176,7 @@
       <c r="B27" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="51"/>
+      <c r="C27" s="50"/>
       <c r="D27" s="40" t="s">
         <v>12</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>45770</v>
       </c>
       <c r="F27" s="23" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="G27" s="23" t="s">
         <v>27</v>
@@ -1220,7 +1220,7 @@
       <c r="B29" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C29" s="51"/>
+      <c r="C29" s="50"/>
       <c r="D29" s="40" t="s">
         <v>12</v>
       </c>
@@ -1248,7 +1248,7 @@
     <row r="31" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
-      <c r="C31" s="51"/>
+      <c r="C31" s="50"/>
       <c r="D31" s="18"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
@@ -1257,6 +1257,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="C10:C11"/>
     <mergeCell ref="C26:C27"/>
     <mergeCell ref="C28:C29"/>
     <mergeCell ref="C30:C31"/>
@@ -1266,12 +1272,6 @@
     <mergeCell ref="C20:C21"/>
     <mergeCell ref="C22:C23"/>
     <mergeCell ref="C24:C25"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="C10:C11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/assets/sched.xlsx
+++ b/assets/sched.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amosca/Documents/Smith/teaching/SDS-CSC235/SDS-CSC235/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB0C2C6B-A930-D343-91B1-02F5E16E249A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF1DE1E3-63DD-E649-80BE-995BAC96874A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1280" yWindow="1300" windowWidth="24200" windowHeight="22180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -82,9 +82,6 @@
     <t>CLASS CANCELED - Rally Day</t>
   </si>
   <si>
-    <t>Final Project Demonstrations</t>
-  </si>
-  <si>
     <t>CLASS CANCELED - Spring Break</t>
   </si>
   <si>
@@ -185,6 +182,9 @@
   </si>
   <si>
     <t xml:space="preserve">Final Project Workshop - User Testing Prep </t>
+  </si>
+  <si>
+    <t>Final Project Demonstrations - 12:15-1:00 Ford 342</t>
   </si>
 </sst>
 </file>
@@ -433,10 +433,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -705,7 +705,7 @@
         <v>45684</v>
       </c>
       <c r="F2" s="45" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G2" s="46"/>
       <c r="H2" s="48"/>
@@ -713,7 +713,7 @@
     <row r="3" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A3" s="14"/>
       <c r="B3" s="16"/>
-      <c r="C3" s="51"/>
+      <c r="C3" s="50"/>
       <c r="D3" s="28" t="s">
         <v>12</v>
       </c>
@@ -721,10 +721,10 @@
         <v>45686</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H3" s="30"/>
     </row>
@@ -749,7 +749,7 @@
     <row r="5" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9"/>
       <c r="B5" s="16"/>
-      <c r="C5" s="51"/>
+      <c r="C5" s="50"/>
       <c r="D5" s="28" t="s">
         <v>12</v>
       </c>
@@ -757,13 +757,13 @@
         <v>45693</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H5" s="31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.15">
@@ -779,14 +779,14 @@
         <v>45698</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G6" s="8"/>
       <c r="H6" s="27"/>
     </row>
     <row r="7" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9"/>
-      <c r="C7" s="51"/>
+      <c r="C7" s="50"/>
       <c r="D7" s="28" t="s">
         <v>12</v>
       </c>
@@ -794,13 +794,13 @@
         <v>45700</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H7" s="31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.15">
@@ -816,14 +816,14 @@
         <v>45705</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G8" s="8"/>
       <c r="H8" s="27"/>
     </row>
     <row r="9" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9"/>
-      <c r="C9" s="51"/>
+      <c r="C9" s="50"/>
       <c r="D9" s="28" t="s">
         <v>12</v>
       </c>
@@ -831,13 +831,13 @@
         <v>45707</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H9" s="31" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.15">
@@ -855,7 +855,7 @@
         <v>45712</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G10" s="8"/>
       <c r="H10" s="27"/>
@@ -867,7 +867,7 @@
       <c r="B11" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="51"/>
+      <c r="C11" s="50"/>
       <c r="D11" s="37" t="s">
         <v>12</v>
       </c>
@@ -878,10 +878,10 @@
         <v>15</v>
       </c>
       <c r="G11" s="24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H11" s="39" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.15">
@@ -897,14 +897,14 @@
         <v>45719</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G12" s="8"/>
       <c r="H12" s="27"/>
     </row>
     <row r="13" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9"/>
-      <c r="C13" s="51"/>
+      <c r="C13" s="50"/>
       <c r="D13" s="28" t="s">
         <v>12</v>
       </c>
@@ -912,7 +912,7 @@
         <v>45721</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G13" s="16"/>
       <c r="H13" s="31"/>
@@ -930,7 +930,7 @@
         <v>45726</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G14" s="8"/>
       <c r="H14" s="27"/>
@@ -938,7 +938,7 @@
     <row r="15" spans="1:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A15" s="14"/>
       <c r="B15" s="16"/>
-      <c r="C15" s="51"/>
+      <c r="C15" s="50"/>
       <c r="D15" s="28" t="s">
         <v>12</v>
       </c>
@@ -946,13 +946,13 @@
         <v>45728</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H15" s="31" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.15">
@@ -972,7 +972,7 @@
         <v>45733</v>
       </c>
       <c r="F16" s="45" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G16" s="46"/>
       <c r="H16" s="47"/>
@@ -984,7 +984,7 @@
       <c r="B17" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="51"/>
+      <c r="C17" s="50"/>
       <c r="D17" s="37" t="s">
         <v>12</v>
       </c>
@@ -992,7 +992,7 @@
         <v>45735</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G17" s="24"/>
       <c r="H17" s="39"/>
@@ -1010,7 +1010,7 @@
         <v>45740</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G18" s="15"/>
       <c r="H18" s="27"/>
@@ -1018,7 +1018,7 @@
     <row r="19" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A19" s="21"/>
       <c r="B19" s="20"/>
-      <c r="C19" s="50"/>
+      <c r="C19" s="51"/>
       <c r="D19" s="34" t="s">
         <v>12</v>
       </c>
@@ -1026,7 +1026,7 @@
         <v>45742</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G19" s="20"/>
       <c r="H19" s="36"/>
@@ -1045,7 +1045,7 @@
         <v>45747</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G20" s="8"/>
       <c r="H20" s="27"/>
@@ -1056,7 +1056,7 @@
       <c r="B21" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="50"/>
+      <c r="C21" s="51"/>
       <c r="D21" s="40" t="s">
         <v>12</v>
       </c>
@@ -1064,13 +1064,13 @@
         <v>45749</v>
       </c>
       <c r="F21" s="23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G21" s="23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H21" s="42" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.15">
@@ -1086,7 +1086,7 @@
         <v>45754</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G22" s="8"/>
       <c r="H22" s="27"/>
@@ -1096,7 +1096,7 @@
       <c r="B23" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C23" s="50"/>
+      <c r="C23" s="51"/>
       <c r="D23" s="40" t="s">
         <v>12</v>
       </c>
@@ -1104,13 +1104,13 @@
         <v>45756</v>
       </c>
       <c r="F23" s="23" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G23" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="H23" s="42" t="s">
         <v>29</v>
-      </c>
-      <c r="H23" s="42" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.15">
@@ -1126,7 +1126,7 @@
         <v>45761</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G24" s="15"/>
       <c r="H24" s="27"/>
@@ -1136,7 +1136,7 @@
       <c r="B25" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="50"/>
+      <c r="C25" s="51"/>
       <c r="D25" s="40" t="s">
         <v>12</v>
       </c>
@@ -1144,13 +1144,13 @@
         <v>45763</v>
       </c>
       <c r="F25" s="23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G25" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="H25" s="42" t="s">
         <v>28</v>
-      </c>
-      <c r="H25" s="42" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.15">
@@ -1166,7 +1166,7 @@
         <v>45768</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G26" s="15"/>
       <c r="H26" s="33"/>
@@ -1176,7 +1176,7 @@
       <c r="B27" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="50"/>
+      <c r="C27" s="51"/>
       <c r="D27" s="40" t="s">
         <v>12</v>
       </c>
@@ -1184,13 +1184,13 @@
         <v>45770</v>
       </c>
       <c r="F27" s="23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G27" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="H27" s="42" t="s">
         <v>27</v>
-      </c>
-      <c r="H27" s="42" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.15">
@@ -1208,7 +1208,7 @@
         <v>45775</v>
       </c>
       <c r="F28" s="32" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G28" s="15"/>
       <c r="H28" s="33"/>
@@ -1220,7 +1220,7 @@
       <c r="B29" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C29" s="50"/>
+      <c r="C29" s="51"/>
       <c r="D29" s="40" t="s">
         <v>12</v>
       </c>
@@ -1228,11 +1228,11 @@
         <v>45777</v>
       </c>
       <c r="F29" s="23" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="G29" s="23"/>
       <c r="H29" s="42" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.15">
@@ -1248,7 +1248,7 @@
     <row r="31" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
-      <c r="C31" s="50"/>
+      <c r="C31" s="51"/>
       <c r="D31" s="18"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
@@ -1257,12 +1257,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="C10:C11"/>
     <mergeCell ref="C26:C27"/>
     <mergeCell ref="C28:C29"/>
     <mergeCell ref="C30:C31"/>
@@ -1272,6 +1266,12 @@
     <mergeCell ref="C20:C21"/>
     <mergeCell ref="C22:C23"/>
     <mergeCell ref="C24:C25"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="C10:C11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
